--- a/reports/pdf_weekly_20261016.xlsx
+++ b/reports/pdf_weekly_20261016.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,947억   ·   현금 410억(8.9%)      주말 2026-10-16  vs  주초 2026-10-12      매수 12종목  /  매도 26종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억   ·   현금 205억(4.6%)      주말 2026-10-16  vs  주초 2026-10-12      매수 12종목  /  매도 26종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>489</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3461384822</v>
+        <v>3464883689</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-310</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2780512652</v>
+        <v>-2783323274</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>139</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>487827213</v>
+        <v>488320323</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-126</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1913510672</v>
+        <v>-1915444904</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>714136154</v>
+        <v>714858023</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-103</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1862990997</v>
+        <v>-1864874162</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>41</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3036130528</v>
+        <v>3039199536</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2127310969</v>
+        <v>-2129461316</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1359962341</v>
+        <v>1361337030</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-74</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3644683233</v>
+        <v>-3648367384</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1475495285</v>
+        <v>1476986758</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-73</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1781454636</v>
+        <v>-1783255382</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1319471360</v>
+        <v>1320805120</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-71</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2888917599</v>
+        <v>-2891837800</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1264031387</v>
+        <v>1265309106</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-46</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-663062079</v>
+        <v>-663732321</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>842687591</v>
+        <v>843539404</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-35</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-864517081</v>
+        <v>-865390960</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>950696539</v>
+        <v>951657530</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-29</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2187700939</v>
+        <v>-2189912330</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1535489256</v>
+        <v>1537041372</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-26</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1469753287</v>
+        <v>-1471238956</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1259774389</v>
+        <v>1261047805</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-23</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-901691563</v>
+        <v>-902603019</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>-21</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-810809607</v>
+        <v>-811629197</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>-20</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-924659552</v>
+        <v>-925594224</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>-15</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1844369106</v>
+        <v>-1846233447</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>-14</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1287593376</v>
+        <v>-1288894912</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>-12</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-468665773</v>
+        <v>-469139514</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>-11</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-879911573</v>
+        <v>-880801013</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>-9</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1314224363</v>
+        <v>-1315552819</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1392,23 +1392,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-386693813</v>
+        <v>-768619786</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.24%</t>
+          <t>1.28%→1.15%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1420,23 +1420,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-767843628</v>
+        <v>-387084694</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>1.28%→1.15%</t>
+          <t>0.34%→0.24%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1214729411</v>
+        <v>-1215957294</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1476,23 +1476,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-861299582</v>
+        <v>-1076226261</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.72%</t>
+          <t>2.56%→2.62%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1504,23 +1504,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1075139479</v>
+        <v>-862170209</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.62%</t>
+          <t>0.98%→0.72%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1532,23 +1532,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-366200822</v>
+        <v>-1027171749</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.39%→0.16%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -1560,30 +1560,30 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1026134502</v>
+        <v>-366570989</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,990억   ·   현금 132억(4.5%)      주말 2026-10-16  vs  주초 2026-10-12      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억   ·   현금 66억(2.3%)      주말 2026-10-16  vs  주초 2026-10-12      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1679,7 +1679,7 @@
         <v>56</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1411284266</v>
+        <v>1411284586</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>-20</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2740100517</v>
+        <v>-2740101137</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>51</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>825766656</v>
+        <v>825766843</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>-19</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-843866159</v>
+        <v>-843866350</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>-14</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2864120540</v>
+        <v>-2864121189</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,556억   ·   현금 77억(3.4%)      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억   ·   현금 39억(1.7%)      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1884,7 +1884,7 @@
         <v>36</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1594253332</v>
+        <v>1591833697</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>-150</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-3914461307</v>
+        <v>-3908520238</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>25</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>3051171019</v>
+        <v>3046540185</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>-39</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2243698049</v>
+        <v>-2240292736</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>21</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2830076445</v>
+        <v>2825781172</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>-30</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-519951174</v>
+        <v>-519162032</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>-25</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-584038945</v>
+        <v>-583152535</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>-20</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-904148302</v>
+        <v>-902776055</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>-6</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1022109341</v>
+        <v>-1020558062</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,913억   ·   현금 81억(4.3%)      주말 2026-10-16  vs  주초 2026-10-12      매수 5종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억   ·   현금 41억(2.2%)      주말 2026-10-16  vs  주초 2026-10-12      매수 5종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -2189,7 +2189,7 @@
         <v>229</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>15971443032</v>
+        <v>15971438028</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>-356</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-4165430965</v>
+        <v>-4165429660</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>125</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>1678018575</v>
+        <v>1678018049</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>-313</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-2895077548</v>
+        <v>-2895076641</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>58</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>905220405</v>
+        <v>905220122</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>-242</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-8091486955</v>
+        <v>-8091484420</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>823124364</v>
+        <v>823124106</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>-238</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1873214504</v>
+        <v>-1873213917</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>15</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>7164014252</v>
+        <v>7164012007</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>-235</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1867603555</v>
+        <v>-1867602970</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>-63</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-986875997</v>
+        <v>-986875688</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>-56</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1797342212</v>
+        <v>-1797341649</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>-34</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-5026491475</v>
+        <v>-5026489900</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>-20</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-1635409829</v>
+        <v>-1635409317</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>-12</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-103869589</v>
+        <v>-103869557</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 296억   ·   현금 7억(2.2%)      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억   ·   현금 3억(1.3%)      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>
@@ -2638,11 +2638,11 @@
         <v>17</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>63897900</v>
+        <v>53191268</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.70%</t>
+          <t>2.32%→2.53%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2659,11 +2659,11 @@
         <v>-88</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-67450240</v>
+        <v>-58901005</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>8.25%→8.02%</t>
+          <t>8.10%→7.87%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2682,11 +2682,11 @@
         <v>8</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>79006400</v>
+        <v>66088761</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.60%</t>
+          <t>2.19%→2.45%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2703,11 +2703,11 @@
         <v>-31</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-54625100</v>
+        <v>-49224871</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.71%</t>
+          <t>2.93%→2.74%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2726,11 +2726,11 @@
         <v>6</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>70028400</v>
+        <v>59294965</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>1.32%→1.56%</t>
+          <t>1.26%→1.48%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2747,11 +2747,11 @@
         <v>-8</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-67643200</v>
+        <v>-64641561</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2.46%→2.23%</t>
+          <t>2.64%→2.39%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="73" ht="19" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억      주말 2026-10-16  vs  주초 2026-10-12      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 994억      주말 2026-10-16  vs  주초 2026-10-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B73" s="4" t="n"/>

--- a/reports/pdf_weekly_20261016.xlsx
+++ b/reports/pdf_weekly_20261016.xlsx
@@ -1392,23 +1392,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-768619786</v>
+        <v>-387084694</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.28%→1.15%</t>
+          <t>0.34%→0.24%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1420,23 +1420,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-387084694</v>
+        <v>-768619786</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.24%</t>
+          <t>1.28%→1.15%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1476,23 +1476,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.62%</t>
+          <t>0.98%→0.72%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1504,23 +1504,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.72%</t>
+          <t>2.56%→2.62%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1532,23 +1532,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1560,23 +1560,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.39%→0.16%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261016.xlsx
+++ b/reports/pdf_weekly_20261016.xlsx
@@ -1532,23 +1532,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.39%→0.16%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -1560,23 +1560,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261016.xlsx
+++ b/reports/pdf_weekly_20261016.xlsx
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1265309106</v>
+        <v>843539404</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.64%</t>
+          <t>1.01%→1.21%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1015,23 +1015,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>843539404</v>
+        <v>1265309106</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.21%</t>
+          <t>3.40%→3.64%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1476,23 +1476,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.72%</t>
+          <t>2.56%→2.62%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1504,23 +1504,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.62%</t>
+          <t>0.98%→0.72%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261016.xlsx
+++ b/reports/pdf_weekly_20261016.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,10 +62,6 @@
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -132,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -175,7 +171,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-10-12 ~ 2026-10-16  (5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
+          <t>주간 변화  ·  2026-10-12 ~ 2026-10-16  (5거래일)  ·  캡처 5/10  ·  대기: RISE, TIGER, DS, TIGER, MIDAS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억   ·   현금 205억(4.6%)      주말 2026-10-16  vs  주초 2026-10-12      매수 12종목  /  매도 26종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억      주말 2026-10-16  vs  주초 2026-10-12      매수 12종목  /  매도 26종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -971,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>843539404</v>
+        <v>1265309106</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.21%</t>
+          <t>3.40%→3.64%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1015,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1265309106</v>
+        <v>843539404</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.64%</t>
+          <t>1.01%→1.21%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1476,23 +1471,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.62%</t>
+          <t>0.98%→0.72%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1504,23 +1499,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.72%</t>
+          <t>2.56%→2.62%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1532,23 +1527,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1560,30 +1555,30 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.39%→0.16%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억   ·   현금 66억(2.3%)      주말 2026-10-16  vs  주초 2026-10-12      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억      주말 2026-10-16  vs  주초 2026-10-12      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1788,7 +1783,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억   ·   현금 39억(1.7%)      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -2093,7 +2088,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억   ·   현금 41억(2.2%)      주말 2026-10-16  vs  주초 2026-10-12      매수 5종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억      주말 2026-10-16  vs  주초 2026-10-12      매수 5종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -2542,7 +2537,7 @@
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억   ·   현금 3억(1.3%)      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억      주말 2026-10-16  vs  주초 2026-10-12      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>
@@ -2778,39 +2773,85 @@
       <c r="K71" s="19" t="n"/>
     </row>
     <row r="73" ht="19" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 994억      주말 2026-10-16  vs  주초 2026-10-12      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="19" t="n"/>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="19" t="n"/>
+      <c r="G73" s="19" t="n"/>
+      <c r="H73" s="19" t="n"/>
+      <c r="I73" s="19" t="n"/>
+      <c r="J73" s="19" t="n"/>
+      <c r="K73" s="19" t="n"/>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="n"/>
+      <c r="C75" s="19" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="19" t="n"/>
+      <c r="G75" s="19" t="n"/>
+      <c r="H75" s="19" t="n"/>
+      <c r="I75" s="19" t="n"/>
+      <c r="J75" s="19" t="n"/>
+      <c r="K75" s="19" t="n"/>
+    </row>
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="19" t="n"/>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="19" t="n"/>
+      <c r="G77" s="19" t="n"/>
+      <c r="H77" s="19" t="n"/>
+      <c r="I77" s="19" t="n"/>
+      <c r="J77" s="19" t="n"/>
+      <c r="K77" s="19" t="n"/>
+    </row>
+    <row r="79" ht="19" customHeight="1">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="n"/>
+      <c r="C79" s="19" t="n"/>
+      <c r="D79" s="19" t="n"/>
+      <c r="E79" s="19" t="n"/>
+      <c r="F79" s="19" t="n"/>
+      <c r="G79" s="19" t="n"/>
+      <c r="H79" s="19" t="n"/>
+      <c r="I79" s="19" t="n"/>
+      <c r="J79" s="19" t="n"/>
+      <c r="K79" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:K77"/>
     <mergeCell ref="A64:K64"/>
     <mergeCell ref="A73:K73"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A79:K79"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="G34:K34"/>

--- a/reports/pdf_weekly_20261016.xlsx
+++ b/reports/pdf_weekly_20261016.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1265309106</v>
+        <v>843539404</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.64%</t>
+          <t>1.01%→1.21%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>843539404</v>
+        <v>1265309106</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.21%</t>
+          <t>3.40%→3.64%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1471,23 +1471,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.72%</t>
+          <t>2.56%→2.62%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1499,23 +1499,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.62%</t>
+          <t>0.98%→0.72%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1527,23 +1527,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.39%→0.16%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -1555,23 +1555,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
